--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd4fa83711e04447"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R23b89e01125e453c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R23b89e01125e453c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05ae9ff38545405f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05ae9ff38545405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ed47ddd7dc24a4e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ed47ddd7dc24a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62896653dbe34cce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62896653dbe34cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf75cb85fb6764e87"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf75cb85fb6764e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R19c8142bdf3a40bc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R19c8142bdf3a40bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c05b8f105da4827"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7c05b8f105da4827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27b809a511604f6c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27b809a511604f6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95c4f40ce40b4fed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95c4f40ce40b4fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca4a9d28b09a48d2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca4a9d28b09a48d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbfb3e77f2b45415e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbfb3e77f2b45415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c05ba96c7ec4625"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c05ba96c7ec4625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R34182aeab9094be0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R34182aeab9094be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87b534f283f6493e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87b534f283f6493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R238a53f309f649e8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R238a53f309f649e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6c7b21614bd4ade"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6c7b21614bd4ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72823d7abc384939"/>
   </x:sheets>
 </x:workbook>
 </file>
